--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_vol_r2/post_rank_positive_return/staggered_10_accounts_hold_10d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_vol_r2/post_rank_positive_return/staggered_10_accounts_hold_10d/close/close_annual_metrics.xlsx
@@ -471,7 +471,7 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.01220890510518924</v>
+        <v>-0.05205862651841842</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2642031920436441</v>
+        <v>0.1592926942190861</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.1273279698023254</v>
+        <v>-0.3929908107974105</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.17687174530484</v>
+        <v>-0.507732736142478</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2403210787102246</v>
+        <v>0.1323891624431379</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.05745448649656938</v>
+        <v>-0.4428335847946955</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>12.51667835594328</v>
+        <v>9.561475558891871</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2020260183779969</v>
+        <v>-0.1771015594272448</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2237866003735495</v>
+        <v>0.2565862480114252</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.004184608734521</v>
+        <v>-0.7208813371110854</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.308357869441788</v>
+        <v>-0.9825179049478664</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.2501152649182075</v>
+        <v>0.2683409737733619</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8373459571367721</v>
+        <v>-0.684588313544505</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>13.1793191656931</v>
+        <v>12.17084950539747</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.04915028880054562</v>
+        <v>0.1039996558891081</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2083662629131993</v>
+        <v>0.1923071538864088</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.2196316031632898</v>
+        <v>0.5540758959688972</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.3152165167322068</v>
+        <v>0.824105290943133</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2064682578781565</v>
+        <v>0.1635384890602437</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.2476336155710354</v>
+        <v>0.6635899860181981</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>13.19284296426923</v>
+        <v>13.0007861278376</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.1077662896400351</v>
+        <v>0.02951385259722539</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2054240724815921</v>
+        <v>0.2272641171018059</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.548585053712624</v>
+        <v>0.1808716740129371</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.8002991795114017</v>
+        <v>0.2576420942693182</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1491774434326925</v>
+        <v>0.1757987409362478</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.7538748949304773</v>
+        <v>0.1749273050929995</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>12.8863226735957</v>
+        <v>15.44937203222312</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.3688331586027926</v>
+        <v>0.5289216395358853</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2440283446415236</v>
+        <v>0.2518590117842264</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.396574097897849</v>
+        <v>1.816778117281652</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.958153652171358</v>
+        <v>2.641860985962285</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1377917388380312</v>
+        <v>0.1355395728842809</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.792932222299861</v>
+        <v>4.081119918756447</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>15.86578711873074</v>
+        <v>14.39509738986491</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.05772891630656796</v>
+        <v>0.1184540241526719</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3369707938666815</v>
+        <v>0.3525893196928814</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.4257167631911298</v>
+        <v>0.7086139135503837</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.6007108021178901</v>
+        <v>1.030682762696822</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2229647138037099</v>
+        <v>0.1552665025258064</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.4803755667277977</v>
+        <v>1.449232946825796</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>13.05441148134301</v>
+        <v>12.61835467069362</v>
       </c>
     </row>
   </sheetData>
